--- a/data/NREL-118/Power_VRES.xlsx
+++ b/data/NREL-118/Power_VRES.xlsx
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U140"/>
+  <dimension ref="A1:U127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.5703125" customWidth="1" min="1" max="1"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Solar_01</t>
+          <t>Solar 01</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -1202,10 +1202,10 @@
         <v/>
       </c>
       <c r="P8" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R8" s="17" t="n">
         <v/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="U8" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Solar_02</t>
+          <t>Solar 02</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1275,10 +1275,10 @@
         <v/>
       </c>
       <c r="P9" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R9" s="17" t="n">
         <v/>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="U9" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Solar_03</t>
+          <t>Solar 03</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1348,10 +1348,10 @@
         <v/>
       </c>
       <c r="P10" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R10" s="17" t="n">
         <v/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="U10" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Solar_04</t>
+          <t>Solar 04</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1421,10 +1421,10 @@
         <v/>
       </c>
       <c r="P11" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R11" s="17" t="n">
         <v/>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="U11" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Solar_05</t>
+          <t>Solar 05</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1494,10 +1494,10 @@
         <v/>
       </c>
       <c r="P12" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R12" s="17" t="n">
         <v/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="U12" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Solar_06</t>
+          <t>Solar 06</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1567,10 +1567,10 @@
         <v/>
       </c>
       <c r="P13" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R13" s="17" t="n">
         <v/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="U13" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Solar_07</t>
+          <t>Solar 07</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1640,10 +1640,10 @@
         <v/>
       </c>
       <c r="P14" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R14" s="17" t="n">
         <v/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="U14" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Solar_08</t>
+          <t>Solar 08</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1713,10 +1713,10 @@
         <v/>
       </c>
       <c r="P15" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R15" s="17" t="n">
         <v/>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="U15" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Solar_09</t>
+          <t>Solar 09</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1786,10 +1786,10 @@
         <v/>
       </c>
       <c r="P16" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R16" s="17" t="n">
         <v/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="U16" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Solar_10</t>
+          <t>Solar 10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -1859,10 +1859,10 @@
         <v/>
       </c>
       <c r="P17" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R17" s="17" t="n">
         <v/>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="U17" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Solar_11</t>
+          <t>Solar 11</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1932,10 +1932,10 @@
         <v/>
       </c>
       <c r="P18" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R18" s="17" t="n">
         <v/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="U18" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Solar_12</t>
+          <t>Solar 12</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -2005,10 +2005,10 @@
         <v/>
       </c>
       <c r="P19" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R19" s="17" t="n">
         <v/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="U19" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Solar_13</t>
+          <t>Solar 13</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -2078,10 +2078,10 @@
         <v/>
       </c>
       <c r="P20" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R20" s="17" t="n">
         <v/>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="U20" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Solar_14</t>
+          <t>Solar 14</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -2151,10 +2151,10 @@
         <v/>
       </c>
       <c r="P21" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R21" s="17" t="n">
         <v/>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="U21" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Solar_15</t>
+          <t>Solar 15</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -2224,10 +2224,10 @@
         <v/>
       </c>
       <c r="P22" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R22" s="17" t="n">
         <v/>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="U22" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Solar_16</t>
+          <t>Solar 16</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -2297,10 +2297,10 @@
         <v/>
       </c>
       <c r="P23" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R23" s="17" t="n">
         <v/>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="U23" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Solar_17</t>
+          <t>Solar 17</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2370,10 +2370,10 @@
         <v/>
       </c>
       <c r="P24" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R24" s="17" t="n">
         <v/>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="U24" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Solar_18</t>
+          <t>Solar 18</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2443,10 +2443,10 @@
         <v/>
       </c>
       <c r="P25" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R25" s="17" t="n">
         <v/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="U25" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Solar_19</t>
+          <t>Solar 19</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2516,10 +2516,10 @@
         <v/>
       </c>
       <c r="P26" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R26" s="17" t="n">
         <v/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="U26" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Solar_20</t>
+          <t>Solar 20</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -2589,10 +2589,10 @@
         <v/>
       </c>
       <c r="P27" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R27" s="17" t="n">
         <v/>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="U27" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Solar_21</t>
+          <t>Solar 21</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -2662,10 +2662,10 @@
         <v/>
       </c>
       <c r="P28" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R28" s="17" t="n">
         <v/>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="U28" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Solar_22</t>
+          <t>Solar 22</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -2735,10 +2735,10 @@
         <v/>
       </c>
       <c r="P29" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R29" s="17" t="n">
         <v/>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="U29" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Solar_23</t>
+          <t>Solar 23</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2808,10 +2808,10 @@
         <v/>
       </c>
       <c r="P30" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R30" s="17" t="n">
         <v/>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="U30" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Solar_24</t>
+          <t>Solar 24</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -2881,10 +2881,10 @@
         <v/>
       </c>
       <c r="P31" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R31" s="17" t="n">
         <v/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="U31" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Solar_25</t>
+          <t>Solar 25</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -2954,10 +2954,10 @@
         <v/>
       </c>
       <c r="P32" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R32" s="17" t="n">
         <v/>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="U32" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Solar_26</t>
+          <t>Solar 26</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -3027,10 +3027,10 @@
         <v/>
       </c>
       <c r="P33" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R33" s="17" t="n">
         <v/>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="U33" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Solar_27</t>
+          <t>Solar 27</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -3100,10 +3100,10 @@
         <v/>
       </c>
       <c r="P34" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R34" s="17" t="n">
         <v/>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="U34" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Solar_28</t>
+          <t>Solar 28</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -3173,10 +3173,10 @@
         <v/>
       </c>
       <c r="P35" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R35" s="17" t="n">
         <v/>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="U35" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Solar_29</t>
+          <t>Solar 29</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -3246,10 +3246,10 @@
         <v/>
       </c>
       <c r="P36" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R36" s="17" t="n">
         <v/>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="U36" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Solar_30</t>
+          <t>Solar 30</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -3319,10 +3319,10 @@
         <v/>
       </c>
       <c r="P37" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R37" s="17" t="n">
         <v/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="U37" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Solar_31</t>
+          <t>Solar 31</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -3392,10 +3392,10 @@
         <v/>
       </c>
       <c r="P38" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R38" s="17" t="n">
         <v/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="U38" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Solar_32</t>
+          <t>Solar 32</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -3465,10 +3465,10 @@
         <v/>
       </c>
       <c r="P39" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R39" s="17" t="n">
         <v/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="U39" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Solar_33</t>
+          <t>Solar 33</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -3538,10 +3538,10 @@
         <v/>
       </c>
       <c r="P40" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R40" s="17" t="n">
         <v/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="U40" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Solar_34</t>
+          <t>Solar 34</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -3611,10 +3611,10 @@
         <v/>
       </c>
       <c r="P41" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R41" s="17" t="n">
         <v/>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="U41" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Solar_35</t>
+          <t>Solar 35</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3684,10 +3684,10 @@
         <v/>
       </c>
       <c r="P42" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R42" s="17" t="n">
         <v/>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="U42" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Solar_36</t>
+          <t>Solar 36</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3757,10 +3757,10 @@
         <v/>
       </c>
       <c r="P43" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R43" s="17" t="n">
         <v/>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="U43" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Solar_37</t>
+          <t>Solar 37</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3830,10 +3830,10 @@
         <v/>
       </c>
       <c r="P44" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R44" s="17" t="n">
         <v/>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="U44" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Solar_38</t>
+          <t>Solar 38</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -3903,10 +3903,10 @@
         <v/>
       </c>
       <c r="P45" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R45" s="17" t="n">
         <v/>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="U45" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Solar_39</t>
+          <t>Solar 39</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3976,10 +3976,10 @@
         <v/>
       </c>
       <c r="P46" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R46" s="17" t="n">
         <v/>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="U46" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Solar_40</t>
+          <t>Solar 40</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -4049,10 +4049,10 @@
         <v/>
       </c>
       <c r="P47" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R47" s="17" t="n">
         <v/>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="U47" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Solar_41</t>
+          <t>Solar 41</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -4122,10 +4122,10 @@
         <v/>
       </c>
       <c r="P48" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R48" s="17" t="n">
         <v/>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="U48" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Solar_42</t>
+          <t>Solar 42</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -4195,10 +4195,10 @@
         <v/>
       </c>
       <c r="P49" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R49" s="17" t="n">
         <v/>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="U49" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Solar_43</t>
+          <t>Solar 43</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -4268,10 +4268,10 @@
         <v/>
       </c>
       <c r="P50" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R50" s="17" t="n">
         <v/>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="U50" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Solar_44</t>
+          <t>Solar 44</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -4341,10 +4341,10 @@
         <v/>
       </c>
       <c r="P51" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R51" s="17" t="n">
         <v/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="U51" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Solar_45</t>
+          <t>Solar 45</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -4414,10 +4414,10 @@
         <v/>
       </c>
       <c r="P52" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R52" s="17" t="n">
         <v/>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="U52" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Solar_46</t>
+          <t>Solar 46</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -4487,10 +4487,10 @@
         <v/>
       </c>
       <c r="P53" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R53" s="17" t="n">
         <v/>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="U53" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Solar_47</t>
+          <t>Solar 47</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -4560,10 +4560,10 @@
         <v/>
       </c>
       <c r="P54" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R54" s="17" t="n">
         <v/>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="U54" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Solar_48</t>
+          <t>Solar 48</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -4633,10 +4633,10 @@
         <v/>
       </c>
       <c r="P55" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q55" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R55" s="17" t="n">
         <v/>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="U55" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>Solar_49</t>
+          <t>Solar 49</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -4706,10 +4706,10 @@
         <v/>
       </c>
       <c r="P56" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q56" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R56" s="17" t="n">
         <v/>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="U56" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Solar_50</t>
+          <t>Solar 50</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -4779,10 +4779,10 @@
         <v/>
       </c>
       <c r="P57" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q57" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R57" s="17" t="n">
         <v/>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="U57" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>Solar_51</t>
+          <t>Solar 51</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -4852,10 +4852,10 @@
         <v/>
       </c>
       <c r="P58" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q58" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R58" s="17" t="n">
         <v/>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="U58" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Solar_52</t>
+          <t>Solar 52</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -4925,10 +4925,10 @@
         <v/>
       </c>
       <c r="P59" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q59" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R59" s="17" t="n">
         <v/>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="U59" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>Solar_53</t>
+          <t>Solar 53</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -4998,10 +4998,10 @@
         <v/>
       </c>
       <c r="P60" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q60" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R60" s="17" t="n">
         <v/>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="U60" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Solar_54</t>
+          <t>Solar 54</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -5071,10 +5071,10 @@
         <v/>
       </c>
       <c r="P61" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q61" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R61" s="17" t="n">
         <v/>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="U61" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Solar_55</t>
+          <t>Solar 55</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -5144,10 +5144,10 @@
         <v/>
       </c>
       <c r="P62" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q62" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R62" s="17" t="n">
         <v/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="U62" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Solar_56</t>
+          <t>Solar 56</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -5217,10 +5217,10 @@
         <v/>
       </c>
       <c r="P63" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q63" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R63" s="17" t="n">
         <v/>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="U63" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>Solar_57</t>
+          <t>Solar 57</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -5290,10 +5290,10 @@
         <v/>
       </c>
       <c r="P64" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q64" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R64" s="17" t="n">
         <v/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="U64" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Solar_58</t>
+          <t>Solar 58</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -5363,10 +5363,10 @@
         <v/>
       </c>
       <c r="P65" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q65" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R65" s="17" t="n">
         <v/>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="U65" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>Solar_59</t>
+          <t>Solar 59</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -5436,10 +5436,10 @@
         <v/>
       </c>
       <c r="P66" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q66" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R66" s="17" t="n">
         <v/>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="U66" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Solar_60</t>
+          <t>Solar 60</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -5509,10 +5509,10 @@
         <v/>
       </c>
       <c r="P67" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q67" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R67" s="17" t="n">
         <v/>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="U67" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>Solar_61</t>
+          <t>Solar 61</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -5582,10 +5582,10 @@
         <v/>
       </c>
       <c r="P68" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q68" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R68" s="17" t="n">
         <v/>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="U68" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Solar_62</t>
+          <t>Solar 62</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -5655,10 +5655,10 @@
         <v/>
       </c>
       <c r="P69" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q69" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R69" s="17" t="n">
         <v/>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="U69" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Solar_63</t>
+          <t>Solar 63</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -5728,10 +5728,10 @@
         <v/>
       </c>
       <c r="P70" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q70" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R70" s="17" t="n">
         <v/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="U70" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Solar_64</t>
+          <t>Solar 64</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -5801,10 +5801,10 @@
         <v/>
       </c>
       <c r="P71" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q71" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R71" s="17" t="n">
         <v/>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="U71" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>Solar_65</t>
+          <t>Solar 65</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -5874,10 +5874,10 @@
         <v/>
       </c>
       <c r="P72" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q72" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R72" s="17" t="n">
         <v/>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="U72" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Solar_66</t>
+          <t>Solar 66</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -5947,10 +5947,10 @@
         <v/>
       </c>
       <c r="P73" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q73" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R73" s="17" t="n">
         <v/>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="U73" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>Solar_67</t>
+          <t>Solar 67</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -6020,10 +6020,10 @@
         <v/>
       </c>
       <c r="P74" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q74" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R74" s="17" t="n">
         <v/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="U74" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Solar_68</t>
+          <t>Solar 68</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -6093,10 +6093,10 @@
         <v/>
       </c>
       <c r="P75" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q75" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R75" s="17" t="n">
         <v/>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="U75" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>Solar_69</t>
+          <t>Solar 69</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -6166,10 +6166,10 @@
         <v/>
       </c>
       <c r="P76" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q76" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R76" s="17" t="n">
         <v/>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="U76" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Solar_70</t>
+          <t>Solar 70</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -6239,10 +6239,10 @@
         <v/>
       </c>
       <c r="P77" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q77" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R77" s="17" t="n">
         <v/>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="U77" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>Solar_71</t>
+          <t>Solar 71</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -6312,10 +6312,10 @@
         <v/>
       </c>
       <c r="P78" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q78" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R78" s="17" t="n">
         <v/>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="U78" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Solar_72</t>
+          <t>Solar 72</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -6385,10 +6385,10 @@
         <v/>
       </c>
       <c r="P79" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q79" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R79" s="17" t="n">
         <v/>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="U79" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>Solar_73</t>
+          <t>Solar 73</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -6458,10 +6458,10 @@
         <v/>
       </c>
       <c r="P80" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q80" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R80" s="17" t="n">
         <v/>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="U80" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Solar_74</t>
+          <t>Solar 74</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -6531,10 +6531,10 @@
         <v/>
       </c>
       <c r="P81" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q81" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R81" s="17" t="n">
         <v/>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="U81" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>Solar_75</t>
+          <t>Solar 75</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -6604,10 +6604,10 @@
         <v/>
       </c>
       <c r="P82" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q82" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R82" s="17" t="n">
         <v/>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="U82" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6677,10 +6677,10 @@
         <v/>
       </c>
       <c r="P83" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q83" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R83" s="17" t="n">
         <v/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="U83" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6750,10 +6750,10 @@
         <v/>
       </c>
       <c r="P84" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q84" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R84" s="17" t="n">
         <v/>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="U84" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6823,10 +6823,10 @@
         <v/>
       </c>
       <c r="P85" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q85" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R85" s="17" t="n">
         <v/>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="U85" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6896,10 +6896,10 @@
         <v/>
       </c>
       <c r="P86" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q86" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R86" s="17" t="n">
         <v/>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="U86" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -6969,10 +6969,10 @@
         <v/>
       </c>
       <c r="P87" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q87" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R87" s="17" t="n">
         <v/>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="U87" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7042,10 +7042,10 @@
         <v/>
       </c>
       <c r="P88" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q88" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R88" s="17" t="n">
         <v/>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="U88" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7115,10 +7115,10 @@
         <v/>
       </c>
       <c r="P89" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q89" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R89" s="17" t="n">
         <v/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="U89" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7188,10 +7188,10 @@
         <v/>
       </c>
       <c r="P90" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q90" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R90" s="17" t="n">
         <v/>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="U90" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7261,10 +7261,10 @@
         <v/>
       </c>
       <c r="P91" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q91" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R91" s="17" t="n">
         <v/>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="U91" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7334,10 +7334,10 @@
         <v/>
       </c>
       <c r="P92" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q92" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R92" s="17" t="n">
         <v/>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="U92" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7407,10 +7407,10 @@
         <v/>
       </c>
       <c r="P93" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q93" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R93" s="17" t="n">
         <v/>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="U93" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7480,10 +7480,10 @@
         <v/>
       </c>
       <c r="P94" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q94" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R94" s="17" t="n">
         <v/>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="U94" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7553,10 +7553,10 @@
         <v/>
       </c>
       <c r="P95" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q95" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R95" s="17" t="n">
         <v/>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="U95" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7626,10 +7626,10 @@
         <v/>
       </c>
       <c r="P96" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q96" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R96" s="17" t="n">
         <v/>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="U96" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7699,10 +7699,10 @@
         <v/>
       </c>
       <c r="P97" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q97" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R97" s="17" t="n">
         <v/>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="U97" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7772,10 +7772,10 @@
         <v/>
       </c>
       <c r="P98" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q98" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R98" s="17" t="n">
         <v/>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="U98" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7845,10 +7845,10 @@
         <v/>
       </c>
       <c r="P99" s="13" t="n">
-        <v>2015</v>
+        <v/>
       </c>
       <c r="Q99" s="13" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="R99" s="17" t="n">
         <v/>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="U99" s="18" t="inlineStr">
         <is>
-          <t>mod-003-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>Hydro 01</t>
+          <t>Hydro 16</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -7884,14 +7884,14 @@
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>bus056</t>
+          <t>bus032</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>69</v>
+        <v>0.8</v>
       </c>
       <c r="H100" s="13" t="n">
         <v>0</v>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="U100" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Hydro 02</t>
+          <t>Hydro 17</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -7957,14 +7957,14 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>bus056</t>
+          <t>bus112</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>69</v>
+        <v>1.35</v>
       </c>
       <c r="H101" s="13" t="n">
         <v>0</v>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="U101" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>Hydro 03</t>
+          <t>Hydro 18</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -8030,14 +8030,14 @@
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>bus066</t>
+          <t>bus112</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>70.84</v>
+        <v>4.65</v>
       </c>
       <c r="H102" s="13" t="n">
         <v>0</v>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="U102" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Hydro 04</t>
+          <t>Hydro 19</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -8103,14 +8103,14 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>bus076</t>
+          <t>bus116</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>70.84</v>
+        <v>648.4400000000001</v>
       </c>
       <c r="H103" s="13" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="U103" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>Hydro 05</t>
+          <t>Hydro 20</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -8176,14 +8176,14 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>bus049</t>
+          <t>bus077</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>75.44</v>
+        <v>765.77</v>
       </c>
       <c r="H104" s="13" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="U104" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Hydro 06</t>
+          <t>Hydro 21</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>bus059</t>
+          <t>bus099</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>112.72852</v>
+        <v>765.77</v>
       </c>
       <c r="H105" s="13" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="U105" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>Hydro 08</t>
+          <t>Hydro 22</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -8322,14 +8322,14 @@
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>bus061</t>
+          <t>bus099</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>112.72852</v>
+        <v>765.77</v>
       </c>
       <c r="H106" s="13" t="n">
         <v>0</v>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="U106" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Hydro 10</t>
+          <t>Hydro 23</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
@@ -8395,14 +8395,14 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>bus062</t>
+          <t>bus069</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>112.72852</v>
+        <v>742.63</v>
       </c>
       <c r="H107" s="13" t="n">
         <v>0</v>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="U107" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>Hydro 11</t>
+          <t>Hydro 24</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -8468,14 +8468,14 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>bus076</t>
+          <t>bus069</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>74.59084</v>
+        <v>742.63</v>
       </c>
       <c r="H108" s="13" t="n">
         <v>0</v>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="U108" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Hydro 12</t>
+          <t>Hydro 25</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -8541,14 +8541,14 @@
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>bus077</t>
+          <t>bus061</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>74.59176000000001</v>
+        <v>286.46</v>
       </c>
       <c r="H109" s="13" t="n">
         <v>0</v>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="U109" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>Hydro 13</t>
+          <t>Hydro 26</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
@@ -8614,14 +8614,14 @@
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>bus059</t>
+          <t>bus116</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>42.96400000000001</v>
+        <v>286.46</v>
       </c>
       <c r="H110" s="13" t="n">
         <v>0</v>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="U110" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Hydro 14</t>
+          <t>Hydro 27</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>bus099</t>
+          <t>bus080</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>101.2</v>
+        <v>286.46</v>
       </c>
       <c r="H111" s="13" t="n">
         <v>0</v>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="U111" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>Hydro 15</t>
+          <t>Hydro 28</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
@@ -8767,7 +8767,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>128.8</v>
+        <v>1116.06</v>
       </c>
       <c r="H112" s="13" t="n">
         <v>0</v>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="U112" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Hydro 16</t>
+          <t>Hydro 29</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
@@ -8833,14 +8833,14 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>bus032</t>
+          <t>bus080</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>0.7360000000000001</v>
+        <v>1116.06</v>
       </c>
       <c r="H113" s="13" t="n">
         <v>0</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="U113" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>Hydro 17</t>
+          <t>Hydro 30</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
@@ -8906,14 +8906,14 @@
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>bus112</t>
+          <t>bus034</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>1.242</v>
+        <v>0.1</v>
       </c>
       <c r="H114" s="13" t="n">
         <v>0</v>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="U114" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Hydro 18</t>
+          <t>Hydro 31</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -8979,14 +8979,14 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>bus112</t>
+          <t>bus034</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>4.278</v>
+        <v>0.4</v>
       </c>
       <c r="H115" s="13" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="U115" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>Hydro 19</t>
+          <t>Hydro 32</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
@@ -9052,14 +9052,14 @@
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>bus116</t>
+          <t>bus034</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>59.65648000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H116" s="13" t="n">
         <v>0</v>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="U116" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Hydro 20</t>
+          <t>Hydro 33</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
@@ -9125,14 +9125,14 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>bus077</t>
+          <t>bus069</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>70.45084</v>
+        <v>1112.39</v>
       </c>
       <c r="H117" s="13" t="n">
         <v>0</v>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="U117" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>Hydro 21</t>
+          <t>Hydro 34</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
@@ -9198,14 +9198,14 @@
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>bus099</t>
+          <t>bus069</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>70.45084</v>
+        <v>1112.39</v>
       </c>
       <c r="H118" s="13" t="n">
         <v>0</v>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="U118" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Hydro 22</t>
+          <t>Hydro 35</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
@@ -9271,14 +9271,14 @@
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>bus099</t>
+          <t>bus034</t>
         </is>
       </c>
       <c r="F119" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>70.45084</v>
+        <v>0.24</v>
       </c>
       <c r="H119" s="13" t="n">
         <v>0</v>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="U119" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>Hydro 23</t>
+          <t>Hydro 36</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
@@ -9344,14 +9344,14 @@
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>bus069</t>
+          <t>bus034</t>
         </is>
       </c>
       <c r="F120" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>68.32196</v>
+        <v>10.76</v>
       </c>
       <c r="H120" s="13" t="n">
         <v>0</v>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="U120" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Hydro 24</t>
+          <t>Hydro 37</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -9417,14 +9417,14 @@
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>bus069</t>
+          <t>bus036</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>68.32196</v>
+        <v>47.1</v>
       </c>
       <c r="H121" s="13" t="n">
         <v>0</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="U121" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>Hydro 25</t>
+          <t>Hydro 38</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
@@ -9490,14 +9490,14 @@
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>bus061</t>
+          <t>bus034</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>26.35432</v>
+        <v>2.46</v>
       </c>
       <c r="H122" s="13" t="n">
         <v>0</v>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="U122" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Hydro 26</t>
+          <t>Hydro 39</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
@@ -9563,14 +9563,14 @@
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>bus116</t>
+          <t>bus034</t>
         </is>
       </c>
       <c r="F123" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>26.35432</v>
+        <v>2.46</v>
       </c>
       <c r="H123" s="13" t="n">
         <v>0</v>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="U123" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>Hydro 27</t>
+          <t>Hydro 40</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
@@ -9636,14 +9636,14 @@
       </c>
       <c r="E124" s="12" t="inlineStr">
         <is>
-          <t>bus080</t>
+          <t>bus065</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>26.35432</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="H124" s="13" t="n">
         <v>0</v>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="U124" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Hydro 28</t>
+          <t>Hydro 41</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
@@ -9709,14 +9709,14 @@
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>bus080</t>
+          <t>bus046</t>
         </is>
       </c>
       <c r="F125" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>102.67752</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="H125" s="13" t="n">
         <v>0</v>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="U125" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>Hydro 29</t>
+          <t>Hydro 42</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
@@ -9782,14 +9782,14 @@
       </c>
       <c r="E126" s="12" t="inlineStr">
         <is>
-          <t>bus080</t>
+          <t>bus042</t>
         </is>
       </c>
       <c r="F126" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>102.67752</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="H126" s="13" t="n">
         <v>0</v>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="U126" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Hydro 30</t>
+          <t>Hydro 43</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
@@ -9855,14 +9855,14 @@
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>bus034</t>
+          <t>bus099</t>
         </is>
       </c>
       <c r="F127" s="13" t="n">
         <v>1</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>0.09200000000000001</v>
+        <v>111.93</v>
       </c>
       <c r="H127" s="13" t="n">
         <v>0</v>
@@ -9907,956 +9907,7 @@
       </c>
       <c r="U127" s="18" t="inlineStr">
         <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="10" t="n"/>
-      <c r="B128" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 31</t>
-        </is>
-      </c>
-      <c r="D128" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E128" s="12" t="inlineStr">
-        <is>
-          <t>bus034</t>
-        </is>
-      </c>
-      <c r="F128" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" s="14" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="H128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L128" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M128" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N128" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O128" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P128" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q128" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R128" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S128" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T128" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U128" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="10" t="n"/>
-      <c r="B129" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 32</t>
-        </is>
-      </c>
-      <c r="D129" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>bus034</t>
-        </is>
-      </c>
-      <c r="F129" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" s="14" t="n">
-        <v>0.4416</v>
-      </c>
-      <c r="H129" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L129" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M129" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N129" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O129" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P129" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q129" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R129" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S129" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T129" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U129" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="10" t="n"/>
-      <c r="B130" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C130" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 33</t>
-        </is>
-      </c>
-      <c r="D130" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E130" s="12" t="inlineStr">
-        <is>
-          <t>bus069</t>
-        </is>
-      </c>
-      <c r="F130" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G130" s="14" t="n">
-        <v>10.233988</v>
-      </c>
-      <c r="H130" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L130" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M130" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N130" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O130" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P130" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q130" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R130" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S130" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T130" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U130" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="10" t="n"/>
-      <c r="B131" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C131" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 34</t>
-        </is>
-      </c>
-      <c r="D131" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="inlineStr">
-        <is>
-          <t>bus069</t>
-        </is>
-      </c>
-      <c r="F131" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="14" t="n">
-        <v>10.233988</v>
-      </c>
-      <c r="H131" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L131" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M131" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N131" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O131" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P131" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q131" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R131" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S131" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T131" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U131" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="10" t="n"/>
-      <c r="B132" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C132" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 35</t>
-        </is>
-      </c>
-      <c r="D132" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E132" s="12" t="inlineStr">
-        <is>
-          <t>bus034</t>
-        </is>
-      </c>
-      <c r="F132" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="14" t="n">
-        <v>0.2208</v>
-      </c>
-      <c r="H132" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L132" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M132" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N132" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O132" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P132" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q132" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R132" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S132" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T132" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U132" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="10" t="n"/>
-      <c r="B133" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C133" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 36</t>
-        </is>
-      </c>
-      <c r="D133" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E133" s="12" t="inlineStr">
-        <is>
-          <t>bus034</t>
-        </is>
-      </c>
-      <c r="F133" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="14" t="n">
-        <v>9.8992</v>
-      </c>
-      <c r="H133" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L133" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M133" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N133" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O133" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P133" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q133" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R133" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S133" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T133" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U133" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="10" t="n"/>
-      <c r="B134" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C134" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 37</t>
-        </is>
-      </c>
-      <c r="D134" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E134" s="12" t="inlineStr">
-        <is>
-          <t>bus036</t>
-        </is>
-      </c>
-      <c r="F134" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="14" t="n">
-        <v>43.332</v>
-      </c>
-      <c r="H134" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L134" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M134" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N134" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O134" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P134" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q134" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R134" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S134" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T134" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U134" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="10" t="n"/>
-      <c r="B135" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C135" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 38</t>
-        </is>
-      </c>
-      <c r="D135" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E135" s="12" t="inlineStr">
-        <is>
-          <t>bus034</t>
-        </is>
-      </c>
-      <c r="F135" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" s="14" t="n">
-        <v>2.2632</v>
-      </c>
-      <c r="H135" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L135" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M135" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N135" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O135" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P135" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q135" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R135" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S135" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T135" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U135" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="10" t="n"/>
-      <c r="B136" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C136" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 39</t>
-        </is>
-      </c>
-      <c r="D136" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E136" s="12" t="inlineStr">
-        <is>
-          <t>bus034</t>
-        </is>
-      </c>
-      <c r="F136" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" s="14" t="n">
-        <v>2.2632</v>
-      </c>
-      <c r="H136" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L136" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M136" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N136" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O136" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P136" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q136" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R136" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S136" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T136" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U136" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="10" t="n"/>
-      <c r="B137" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C137" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 40</t>
-        </is>
-      </c>
-      <c r="D137" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E137" s="12" t="inlineStr">
-        <is>
-          <t>bus065</t>
-        </is>
-      </c>
-      <c r="F137" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="14" t="n">
-        <v>89.17560000000002</v>
-      </c>
-      <c r="H137" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L137" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M137" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N137" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O137" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P137" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q137" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R137" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S137" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T137" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U137" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="10" t="n"/>
-      <c r="B138" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C138" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 41</t>
-        </is>
-      </c>
-      <c r="D138" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E138" s="12" t="inlineStr">
-        <is>
-          <t>bus046</t>
-        </is>
-      </c>
-      <c r="F138" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="14" t="n">
-        <v>88.5592</v>
-      </c>
-      <c r="H138" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L138" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M138" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N138" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O138" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P138" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q138" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R138" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S138" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T138" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U138" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="10" t="n"/>
-      <c r="B139" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C139" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 42</t>
-        </is>
-      </c>
-      <c r="D139" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E139" s="12" t="inlineStr">
-        <is>
-          <t>bus042</t>
-        </is>
-      </c>
-      <c r="F139" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" s="14" t="n">
-        <v>88.5592</v>
-      </c>
-      <c r="H139" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L139" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M139" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N139" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O139" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P139" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q139" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R139" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S139" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T139" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U139" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="10" t="n"/>
-      <c r="B140" s="11" t="n">
-        <v/>
-      </c>
-      <c r="C140" s="12" t="inlineStr">
-        <is>
-          <t>Hydro 43</t>
-        </is>
-      </c>
-      <c r="D140" s="12" t="inlineStr">
-        <is>
-          <t>RoR</t>
-        </is>
-      </c>
-      <c r="E140" s="12" t="inlineStr">
-        <is>
-          <t>bus099</t>
-        </is>
-      </c>
-      <c r="F140" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="14" t="n">
-        <v>102.9756</v>
-      </c>
-      <c r="H140" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L140" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M140" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N140" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O140" s="14" t="n">
-        <v/>
-      </c>
-      <c r="P140" s="13" t="n">
-        <v/>
-      </c>
-      <c r="Q140" s="13" t="n">
-        <v/>
-      </c>
-      <c r="R140" s="17" t="n">
-        <v/>
-      </c>
-      <c r="S140" s="17" t="n">
-        <v/>
-      </c>
-      <c r="T140" s="18" t="inlineStr">
-        <is>
-          <t>NREL-118-mod</t>
-        </is>
-      </c>
-      <c r="U140" s="18" t="inlineStr">
-        <is>
-          <t>mod-005-A</t>
+          <t>vres-generators</t>
         </is>
       </c>
     </row>

--- a/data/NREL-118/Power_VRES.xlsx
+++ b/data/NREL-118/Power_VRES.xlsx
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>746.76</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>0.01</v>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>369.26</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K9" s="15" t="n">
         <v>0.01</v>
@@ -1318,19 +1318,19 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>264.47</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>0.01</v>
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>4.85</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K11" s="15" t="n">
         <v>0.01</v>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>0.12</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K12" s="15" t="n">
         <v>0.01</v>
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>6.33</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K13" s="15" t="n">
         <v>0.01</v>
@@ -1610,19 +1610,19 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>0.21</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K14" s="15" t="n">
         <v>0.01</v>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>2.51</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K15" s="15" t="n">
         <v>0.01</v>
@@ -1756,19 +1756,19 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>12.85</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K16" s="15" t="n">
         <v>0.01</v>
@@ -1829,19 +1829,19 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>9.710000000000001</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K17" s="15" t="n">
         <v>0.01</v>
@@ -1902,19 +1902,19 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>1.98</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K18" s="15" t="n">
         <v>0.01</v>
@@ -1975,19 +1975,19 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>1.54</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K19" s="15" t="n">
         <v>0.01</v>
@@ -2048,19 +2048,19 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>0.26</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K20" s="15" t="n">
         <v>0.01</v>
@@ -2121,19 +2121,19 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>11.71</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K21" s="15" t="n">
         <v>0.01</v>
@@ -2194,19 +2194,19 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>10.53</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K22" s="15" t="n">
         <v>0.01</v>
@@ -2267,19 +2267,19 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>6.6</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K23" s="15" t="n">
         <v>0.01</v>
@@ -2340,19 +2340,19 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>3.01</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K24" s="15" t="n">
         <v>0.01</v>
@@ -2413,19 +2413,19 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>12.35</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K25" s="15" t="n">
         <v>0.01</v>
@@ -2486,19 +2486,19 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>0.1</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K26" s="15" t="n">
         <v>0.01</v>
@@ -2559,19 +2559,19 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>10.08</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K27" s="15" t="n">
         <v>0.01</v>
@@ -2632,19 +2632,19 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>18.42</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K28" s="15" t="n">
         <v>0.01</v>
@@ -2705,19 +2705,19 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>8.98</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K29" s="15" t="n">
         <v>0.01</v>
@@ -2778,19 +2778,19 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>0.29</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K30" s="15" t="n">
         <v>0.01</v>
@@ -2851,19 +2851,19 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>1.45</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K31" s="15" t="n">
         <v>0.01</v>
@@ -2924,19 +2924,19 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>1.94</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K32" s="15" t="n">
         <v>0.01</v>
@@ -2997,19 +2997,19 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>1.8</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K33" s="15" t="n">
         <v>0.01</v>
@@ -3070,19 +3070,19 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>1.13</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K34" s="15" t="n">
         <v>0.01</v>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>8.029999999999999</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K35" s="15" t="n">
         <v>0.01</v>
@@ -3216,19 +3216,19 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>8.630000000000001</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K36" s="15" t="n">
         <v>0.01</v>
@@ -3289,19 +3289,19 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>4.5</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K37" s="15" t="n">
         <v>0.01</v>
@@ -3362,19 +3362,19 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>116.03</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K38" s="15" t="n">
         <v>0.01</v>
@@ -3435,19 +3435,19 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>173.97</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K39" s="15" t="n">
         <v>0.01</v>
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>132</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K40" s="15" t="n">
         <v>0.01</v>
@@ -3581,19 +3581,19 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>125</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K41" s="15" t="n">
         <v>0.01</v>
@@ -3654,19 +3654,19 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>45</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K42" s="15" t="n">
         <v>0.01</v>
@@ -3727,19 +3727,19 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>128.9</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K43" s="15" t="n">
         <v>0.01</v>
@@ -3800,19 +3800,19 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>26</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K44" s="15" t="n">
         <v>0.01</v>
@@ -3873,19 +3873,19 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>20</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K45" s="15" t="n">
         <v>0.01</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K46" s="15" t="n">
         <v>0.01</v>
@@ -4019,19 +4019,19 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K47" s="15" t="n">
         <v>0.01</v>
@@ -4092,19 +4092,19 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K48" s="15" t="n">
         <v>0.01</v>
@@ -4165,19 +4165,19 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="H49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K49" s="15" t="n">
         <v>0.01</v>
@@ -4238,19 +4238,19 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K50" s="15" t="n">
         <v>0.01</v>
@@ -4311,19 +4311,19 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K51" s="15" t="n">
         <v>0.01</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K52" s="15" t="n">
         <v>0.01</v>
@@ -4457,19 +4457,19 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K53" s="15" t="n">
         <v>0.01</v>
@@ -4530,19 +4530,19 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K54" s="15" t="n">
         <v>0.01</v>
@@ -4603,19 +4603,19 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K55" s="15" t="n">
         <v>0.01</v>
@@ -4676,19 +4676,19 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="14" t="n">
         <v>1.1</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K56" s="15" t="n">
         <v>0.01</v>
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>4.69</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K57" s="15" t="n">
         <v>0.01</v>
@@ -4822,19 +4822,19 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="14" t="n">
         <v>15.65</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K58" s="15" t="n">
         <v>0.01</v>
@@ -4895,19 +4895,19 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="14" t="n">
         <v>10.64</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K59" s="15" t="n">
         <v>0.01</v>
@@ -4968,19 +4968,19 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="14" t="n">
         <v>16.09</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K60" s="15" t="n">
         <v>0.01</v>
@@ -5041,19 +5041,19 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K61" s="15" t="n">
         <v>0.01</v>
@@ -5114,19 +5114,19 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" s="14" t="n">
         <v>20.01</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K62" s="15" t="n">
         <v>0.01</v>
@@ -5187,19 +5187,19 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" s="14" t="n">
         <v>20.07</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K63" s="15" t="n">
         <v>0.01</v>
@@ -5260,19 +5260,19 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" s="14" t="n">
         <v>6.84</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K64" s="15" t="n">
         <v>0.01</v>
@@ -5333,19 +5333,19 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" s="14" t="n">
         <v>8.01</v>
       </c>
       <c r="H65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K65" s="15" t="n">
         <v>0.01</v>
@@ -5406,19 +5406,19 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="14" t="n">
         <v>12.42</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K66" s="15" t="n">
         <v>0.01</v>
@@ -5479,19 +5479,19 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" s="14" t="n">
         <v>15.89</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K67" s="15" t="n">
         <v>0.01</v>
@@ -5552,19 +5552,19 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="14" t="n">
         <v>1.97</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K68" s="15" t="n">
         <v>0.01</v>
@@ -5625,19 +5625,19 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="H69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K69" s="15" t="n">
         <v>0.01</v>
@@ -5698,19 +5698,19 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>60</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K70" s="15" t="n">
         <v>0.01</v>
@@ -5771,19 +5771,19 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="14" t="n">
         <v>21</v>
       </c>
       <c r="H71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K71" s="15" t="n">
         <v>0.01</v>
@@ -5844,19 +5844,19 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="14" t="n">
         <v>64.8</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K72" s="15" t="n">
         <v>0.01</v>
@@ -5917,19 +5917,19 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>123.5</v>
       </c>
       <c r="H73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K73" s="15" t="n">
         <v>0.01</v>
@@ -5990,19 +5990,19 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="14" t="n">
         <v>40</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K74" s="15" t="n">
         <v>0.01</v>
@@ -6063,19 +6063,19 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="14" t="n">
         <v>96</v>
       </c>
       <c r="H75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K75" s="15" t="n">
         <v>0.01</v>
@@ -6136,19 +6136,19 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="14" t="n">
         <v>123</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K76" s="15" t="n">
         <v>0.01</v>
@@ -6209,19 +6209,19 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="14" t="n">
         <v>150</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K77" s="15" t="n">
         <v>0.01</v>
@@ -6282,19 +6282,19 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="14" t="n">
         <v>104.99</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K78" s="15" t="n">
         <v>0.01</v>
@@ -6355,19 +6355,19 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="14" t="n">
         <v>25.2</v>
       </c>
       <c r="H79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K79" s="15" t="n">
         <v>0.01</v>
@@ -6428,19 +6428,19 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" s="14" t="n">
         <v>25</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K80" s="15" t="n">
         <v>0.01</v>
@@ -6501,19 +6501,19 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" s="14" t="n">
         <v>25</v>
       </c>
       <c r="H81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K81" s="15" t="n">
         <v>0.01</v>
@@ -6574,19 +6574,19 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" s="14" t="n">
         <v>30</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" s="15" t="n">
-        <v>0</v>
+        <v>38283.38018933929</v>
       </c>
       <c r="K82" s="15" t="n">
         <v>0.01</v>
@@ -6647,19 +6647,19 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>11.5</v>
       </c>
       <c r="H83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K83" s="15" t="n">
         <v>0.05</v>
@@ -6720,19 +6720,19 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>38</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K84" s="15" t="n">
         <v>0.05</v>
@@ -6793,19 +6793,19 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="14" t="n">
         <v>10</v>
       </c>
       <c r="H85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K85" s="15" t="n">
         <v>0.05</v>
@@ -6866,19 +6866,19 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="14" t="n">
         <v>5</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K86" s="15" t="n">
         <v>0.05</v>
@@ -6939,19 +6939,19 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="14" t="n">
         <v>1.1</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K87" s="15" t="n">
         <v>0.05</v>
@@ -7012,19 +7012,19 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" s="14" t="n">
         <v>24.1</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K88" s="15" t="n">
         <v>0.05</v>
@@ -7085,19 +7085,19 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" s="14" t="n">
         <v>16.6</v>
       </c>
       <c r="H89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K89" s="15" t="n">
         <v>0.05</v>
@@ -7158,19 +7158,19 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" s="14" t="n">
         <v>16.6</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K90" s="15" t="n">
         <v>0.05</v>
@@ -7231,19 +7231,19 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" s="14" t="n">
         <v>16.6</v>
       </c>
       <c r="H91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K91" s="15" t="n">
         <v>0.05</v>
@@ -7304,19 +7304,19 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" s="14" t="n">
         <v>16.6</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K92" s="15" t="n">
         <v>0.05</v>
@@ -7377,19 +7377,19 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="14" t="n">
         <v>16.6</v>
       </c>
       <c r="H93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K93" s="15" t="n">
         <v>0.05</v>
@@ -7450,19 +7450,19 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="14" t="n">
         <v>97.5</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K94" s="15" t="n">
         <v>0.05</v>
@@ -7523,19 +7523,19 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="14" t="n">
         <v>58.7</v>
       </c>
       <c r="H95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K95" s="15" t="n">
         <v>0.05</v>
@@ -7596,19 +7596,19 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="14" t="n">
         <v>400</v>
       </c>
       <c r="H96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K96" s="15" t="n">
         <v>0.05</v>
@@ -7669,19 +7669,19 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="14" t="n">
         <v>50</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K97" s="15" t="n">
         <v>0.05</v>
@@ -7742,19 +7742,19 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="14" t="n">
         <v>149.5</v>
       </c>
       <c r="H98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K98" s="15" t="n">
         <v>0.05</v>
@@ -7815,19 +7815,19 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" s="14" t="n">
         <v>149.5</v>
       </c>
       <c r="H99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>0</v>
+        <v>101644.123323877</v>
       </c>
       <c r="K99" s="15" t="n">
         <v>0.05</v>

--- a/data/NREL-118/Power_VRES.xlsx
+++ b/data/NREL-118/Power_VRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FelixAuer\Git\LEGO-Pyomo\data\NREL-118\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849F1623-ABA0-43A6-A7ED-359ED923BCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E7F234-070B-4EE4-B0F7-FC09BD881AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34230" yWindow="-21705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4170" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -6146,16 +6146,16 @@
         <v>74</v>
       </c>
       <c r="F100" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="14">
         <v>0.8</v>
       </c>
       <c r="H100" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="15">
         <f>2336*1000/100</f>
@@ -6194,16 +6194,16 @@
         <v>119</v>
       </c>
       <c r="F101" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="14">
         <v>1.35</v>
       </c>
       <c r="H101" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" s="15">
         <f t="shared" ref="J101:J127" si="4">2336*1000/100</f>
@@ -6242,16 +6242,16 @@
         <v>119</v>
       </c>
       <c r="F102" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="14">
         <v>4.6500000000000004</v>
       </c>
       <c r="H102" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J102" s="15">
         <f t="shared" si="4"/>
@@ -6290,16 +6290,16 @@
         <v>191</v>
       </c>
       <c r="F103" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" s="14">
         <v>648.44000000000005</v>
       </c>
       <c r="H103" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" s="15">
         <f t="shared" si="4"/>
@@ -6338,16 +6338,16 @@
         <v>193</v>
       </c>
       <c r="F104" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" s="14">
         <v>765.77</v>
       </c>
       <c r="H104" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" s="15">
         <f t="shared" si="4"/>
@@ -6386,16 +6386,16 @@
         <v>195</v>
       </c>
       <c r="F105" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" s="14">
         <v>765.77</v>
       </c>
       <c r="H105" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="15">
         <f t="shared" si="4"/>
@@ -6434,16 +6434,16 @@
         <v>195</v>
       </c>
       <c r="F106" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" s="14">
         <v>765.77</v>
       </c>
       <c r="H106" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="15">
         <f t="shared" si="4"/>
@@ -6482,16 +6482,16 @@
         <v>146</v>
       </c>
       <c r="F107" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" s="14">
         <v>742.63</v>
       </c>
       <c r="H107" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" s="15">
         <f t="shared" si="4"/>
@@ -6530,16 +6530,16 @@
         <v>146</v>
       </c>
       <c r="F108" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" s="14">
         <v>742.63</v>
       </c>
       <c r="H108" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" s="15">
         <f t="shared" si="4"/>
@@ -6578,16 +6578,16 @@
         <v>200</v>
       </c>
       <c r="F109" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" s="14">
         <v>286.45999999999998</v>
       </c>
       <c r="H109" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="15">
         <f t="shared" si="4"/>
@@ -6626,16 +6626,16 @@
         <v>191</v>
       </c>
       <c r="F110" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="14">
         <v>286.45999999999998</v>
       </c>
       <c r="H110" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="15">
         <f t="shared" si="4"/>
@@ -6674,16 +6674,16 @@
         <v>203</v>
       </c>
       <c r="F111" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" s="14">
         <v>286.45999999999998</v>
       </c>
       <c r="H111" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="15">
         <f t="shared" si="4"/>
@@ -6722,16 +6722,16 @@
         <v>203</v>
       </c>
       <c r="F112" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" s="14">
         <v>1116.06</v>
       </c>
       <c r="H112" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" s="15">
         <f t="shared" si="4"/>
@@ -6770,16 +6770,16 @@
         <v>203</v>
       </c>
       <c r="F113" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" s="14">
         <v>1116.06</v>
       </c>
       <c r="H113" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" s="15">
         <f t="shared" si="4"/>
@@ -6818,16 +6818,16 @@
         <v>207</v>
       </c>
       <c r="F114" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" s="14">
         <v>0.1</v>
       </c>
       <c r="H114" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" s="15">
         <f t="shared" si="4"/>
@@ -6866,16 +6866,16 @@
         <v>207</v>
       </c>
       <c r="F115" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" s="14">
         <v>0.4</v>
       </c>
       <c r="H115" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="15">
         <f t="shared" si="4"/>
@@ -6914,16 +6914,16 @@
         <v>207</v>
       </c>
       <c r="F116" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" s="14">
         <v>0.48</v>
       </c>
       <c r="H116" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" s="15">
         <f t="shared" si="4"/>
@@ -6962,16 +6962,16 @@
         <v>146</v>
       </c>
       <c r="F117" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" s="14">
         <v>1112.3900000000001</v>
       </c>
       <c r="H117" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" s="15">
         <f t="shared" si="4"/>
@@ -7010,16 +7010,16 @@
         <v>146</v>
       </c>
       <c r="F118" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" s="14">
         <v>1112.3900000000001</v>
       </c>
       <c r="H118" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" s="15">
         <f t="shared" si="4"/>
@@ -7058,16 +7058,16 @@
         <v>207</v>
       </c>
       <c r="F119" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" s="14">
         <v>0.24</v>
       </c>
       <c r="H119" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" s="15">
         <f t="shared" si="4"/>
@@ -7106,16 +7106,16 @@
         <v>207</v>
       </c>
       <c r="F120" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" s="14">
         <v>10.76</v>
       </c>
       <c r="H120" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="15">
         <f t="shared" si="4"/>
@@ -7154,16 +7154,16 @@
         <v>215</v>
       </c>
       <c r="F121" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" s="14">
         <v>47.1</v>
       </c>
       <c r="H121" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="15">
         <f t="shared" si="4"/>
@@ -7202,16 +7202,16 @@
         <v>207</v>
       </c>
       <c r="F122" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="14">
         <v>2.46</v>
       </c>
       <c r="H122" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" s="15">
         <f t="shared" si="4"/>
@@ -7250,16 +7250,16 @@
         <v>207</v>
       </c>
       <c r="F123" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" s="14">
         <v>2.46</v>
       </c>
       <c r="H123" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123" s="15">
         <f t="shared" si="4"/>
@@ -7298,16 +7298,16 @@
         <v>219</v>
       </c>
       <c r="F124" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" s="14">
         <v>96.93</v>
       </c>
       <c r="H124" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" s="15">
         <f t="shared" si="4"/>
@@ -7346,16 +7346,16 @@
         <v>221</v>
       </c>
       <c r="F125" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" s="14">
         <v>96.26</v>
       </c>
       <c r="H125" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" s="15">
         <f t="shared" si="4"/>
@@ -7394,16 +7394,16 @@
         <v>223</v>
       </c>
       <c r="F126" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" s="14">
         <v>96.26</v>
       </c>
       <c r="H126" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I126" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="15">
         <f t="shared" si="4"/>
@@ -7442,16 +7442,16 @@
         <v>195</v>
       </c>
       <c r="F127" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" s="14">
         <v>111.93</v>
       </c>
       <c r="H127" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" s="15">
         <f t="shared" si="4"/>

--- a/data/NREL-118/Power_VRES.xlsx
+++ b/data/NREL-118/Power_VRES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FelixAuer\Git\LEGO-Pyomo\data\NREL-118\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E7F234-070B-4EE4-B0F7-FC09BD881AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A78F62-D195-4F96-BCD9-181F48C72923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4170" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -828,26 +828,31 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1650,18 +1655,16 @@
         <v>1</v>
       </c>
       <c r="J8" s="15">
-        <f>AVERAGE(900,1600)*1000/30</f>
-        <v>41666.666666666664</v>
+        <v>41840.095813545537</v>
       </c>
       <c r="K8" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L8" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
+      <c r="N8" s="16"/>
       <c r="O8" s="14"/>
       <c r="P8" s="13"/>
       <c r="Q8" s="13"/>
@@ -1699,18 +1702,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" ref="J9:J72" si="0">AVERAGE(900,1600)*1000/30</f>
-        <v>41666.666666666664</v>
+        <v>41630.722672909083</v>
       </c>
       <c r="K9" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L9" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
+      <c r="N9" s="16"/>
       <c r="O9" s="14"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
@@ -1748,18 +1749,16 @@
         <v>1</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41766.552458130172</v>
       </c>
       <c r="K10" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L10" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
+      <c r="N10" s="16"/>
       <c r="O10" s="14"/>
       <c r="P10" s="13"/>
       <c r="Q10" s="13"/>
@@ -1797,18 +1796,16 @@
         <v>1</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41817.157089353357</v>
       </c>
       <c r="K11" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L11" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
+      <c r="N11" s="16"/>
       <c r="O11" s="14"/>
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
@@ -1846,18 +1843,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41804.950606176106</v>
       </c>
       <c r="K12" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L12" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
+      <c r="N12" s="16"/>
       <c r="O12" s="14"/>
       <c r="P12" s="13"/>
       <c r="Q12" s="13"/>
@@ -1895,18 +1890,16 @@
         <v>1</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41579.703225842757</v>
       </c>
       <c r="K13" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L13" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
+      <c r="N13" s="16"/>
       <c r="O13" s="14"/>
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
@@ -1944,18 +1937,16 @@
         <v>1</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41867.379924459347</v>
       </c>
       <c r="K14" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L14" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
+      <c r="N14" s="16"/>
       <c r="O14" s="14"/>
       <c r="P14" s="13"/>
       <c r="Q14" s="13"/>
@@ -1993,18 +1984,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41825.113496877544</v>
       </c>
       <c r="K15" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L15" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
+      <c r="N15" s="16"/>
       <c r="O15" s="14"/>
       <c r="P15" s="13"/>
       <c r="Q15" s="13"/>
@@ -2042,18 +2031,16 @@
         <v>1</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41738.451016197236</v>
       </c>
       <c r="K16" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L16" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
+      <c r="N16" s="16"/>
       <c r="O16" s="14"/>
       <c r="P16" s="13"/>
       <c r="Q16" s="13"/>
@@ -2091,18 +2078,16 @@
         <v>1</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41506.062929528503</v>
       </c>
       <c r="K17" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L17" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
+      <c r="N17" s="16"/>
       <c r="O17" s="14"/>
       <c r="P17" s="13"/>
       <c r="Q17" s="13"/>
@@ -2140,18 +2125,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41751.421709737988</v>
       </c>
       <c r="K18" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L18" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
+      <c r="N18" s="16"/>
       <c r="O18" s="14"/>
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
@@ -2189,18 +2172,16 @@
         <v>1</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41620.087105942468</v>
       </c>
       <c r="K19" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L19" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
+      <c r="N19" s="16"/>
       <c r="O19" s="14"/>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
@@ -2238,18 +2219,16 @@
         <v>1</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41722.567627426812</v>
       </c>
       <c r="K20" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L20" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
+      <c r="N20" s="16"/>
       <c r="O20" s="14"/>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
@@ -2287,18 +2266,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41804.983994772068</v>
       </c>
       <c r="K21" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L21" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
+      <c r="N21" s="16"/>
       <c r="O21" s="14"/>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
@@ -2336,18 +2313,16 @@
         <v>1</v>
       </c>
       <c r="J22" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41790.729812377016</v>
       </c>
       <c r="K22" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L22" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
+      <c r="N22" s="16"/>
       <c r="O22" s="14"/>
       <c r="P22" s="13"/>
       <c r="Q22" s="13"/>
@@ -2385,18 +2360,16 @@
         <v>1</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41871.803344528067</v>
       </c>
       <c r="K23" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L23" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
+      <c r="N23" s="16"/>
       <c r="O23" s="14"/>
       <c r="P23" s="13"/>
       <c r="Q23" s="13"/>
@@ -2434,18 +2407,16 @@
         <v>1</v>
       </c>
       <c r="J24" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41653.612015144812</v>
       </c>
       <c r="K24" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L24" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="N24" s="16"/>
       <c r="O24" s="14"/>
       <c r="P24" s="13"/>
       <c r="Q24" s="13"/>
@@ -2483,18 +2454,16 @@
         <v>1</v>
       </c>
       <c r="J25" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41600.804854234586</v>
       </c>
       <c r="K25" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L25" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
+      <c r="N25" s="16"/>
       <c r="O25" s="14"/>
       <c r="P25" s="13"/>
       <c r="Q25" s="13"/>
@@ -2532,18 +2501,16 @@
         <v>1</v>
       </c>
       <c r="J26" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41769.392364500753</v>
       </c>
       <c r="K26" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L26" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
+      <c r="N26" s="16"/>
       <c r="O26" s="14"/>
       <c r="P26" s="13"/>
       <c r="Q26" s="13"/>
@@ -2581,18 +2548,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41692.331175479892</v>
       </c>
       <c r="K27" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L27" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
+      <c r="N27" s="16"/>
       <c r="O27" s="14"/>
       <c r="P27" s="13"/>
       <c r="Q27" s="13"/>
@@ -2630,18 +2595,16 @@
         <v>1</v>
       </c>
       <c r="J28" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41655.386915130563</v>
       </c>
       <c r="K28" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L28" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
+      <c r="N28" s="16"/>
       <c r="O28" s="14"/>
       <c r="P28" s="13"/>
       <c r="Q28" s="13"/>
@@ -2679,18 +2642,16 @@
         <v>1</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41663.178228536643</v>
       </c>
       <c r="K29" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L29" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
+      <c r="N29" s="16"/>
       <c r="O29" s="14"/>
       <c r="P29" s="13"/>
       <c r="Q29" s="13"/>
@@ -2728,18 +2689,16 @@
         <v>1</v>
       </c>
       <c r="J30" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41612.991756721109</v>
       </c>
       <c r="K30" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L30" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
+      <c r="N30" s="16"/>
       <c r="O30" s="14"/>
       <c r="P30" s="13"/>
       <c r="Q30" s="13"/>
@@ -2777,18 +2736,16 @@
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41758.213168697097</v>
       </c>
       <c r="K31" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L31" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
+      <c r="N31" s="16"/>
       <c r="O31" s="14"/>
       <c r="P31" s="13"/>
       <c r="Q31" s="13"/>
@@ -2826,18 +2783,16 @@
         <v>1</v>
       </c>
       <c r="J32" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41651.869071050285</v>
       </c>
       <c r="K32" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L32" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
+      <c r="N32" s="16"/>
       <c r="O32" s="14"/>
       <c r="P32" s="13"/>
       <c r="Q32" s="13"/>
@@ -2875,18 +2830,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41601.536344830223</v>
       </c>
       <c r="K33" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L33" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
+      <c r="N33" s="16"/>
       <c r="O33" s="14"/>
       <c r="P33" s="13"/>
       <c r="Q33" s="13"/>
@@ -2924,18 +2877,16 @@
         <v>1</v>
       </c>
       <c r="J34" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41702.052480945335</v>
       </c>
       <c r="K34" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L34" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
+      <c r="N34" s="16"/>
       <c r="O34" s="14"/>
       <c r="P34" s="13"/>
       <c r="Q34" s="13"/>
@@ -2973,18 +2924,16 @@
         <v>1</v>
       </c>
       <c r="J35" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41680.764627630735</v>
       </c>
       <c r="K35" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L35" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
+      <c r="N35" s="16"/>
       <c r="O35" s="14"/>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
@@ -3022,18 +2971,16 @@
         <v>1</v>
       </c>
       <c r="J36" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41736.269123121936</v>
       </c>
       <c r="K36" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L36" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
+      <c r="N36" s="16"/>
       <c r="O36" s="14"/>
       <c r="P36" s="13"/>
       <c r="Q36" s="13"/>
@@ -3071,18 +3018,16 @@
         <v>1</v>
       </c>
       <c r="J37" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41493.061978546823</v>
       </c>
       <c r="K37" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L37" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
+      <c r="N37" s="16"/>
       <c r="O37" s="14"/>
       <c r="P37" s="13"/>
       <c r="Q37" s="13"/>
@@ -3120,18 +3065,16 @@
         <v>1</v>
       </c>
       <c r="J38" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41543.090991471494</v>
       </c>
       <c r="K38" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L38" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
+      <c r="N38" s="16"/>
       <c r="O38" s="14"/>
       <c r="P38" s="13"/>
       <c r="Q38" s="13"/>
@@ -3169,18 +3112,16 @@
         <v>1</v>
       </c>
       <c r="J39" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41776.832700232742</v>
       </c>
       <c r="K39" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L39" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
+      <c r="N39" s="16"/>
       <c r="O39" s="14"/>
       <c r="P39" s="13"/>
       <c r="Q39" s="13"/>
@@ -3218,18 +3159,16 @@
         <v>1</v>
       </c>
       <c r="J40" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41735.384136782661</v>
       </c>
       <c r="K40" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L40" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
+      <c r="N40" s="16"/>
       <c r="O40" s="14"/>
       <c r="P40" s="13"/>
       <c r="Q40" s="13"/>
@@ -3267,18 +3206,16 @@
         <v>1</v>
       </c>
       <c r="J41" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41851.650862521878</v>
       </c>
       <c r="K41" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L41" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
+      <c r="N41" s="16"/>
       <c r="O41" s="14"/>
       <c r="P41" s="13"/>
       <c r="Q41" s="13"/>
@@ -3316,18 +3253,16 @@
         <v>1</v>
       </c>
       <c r="J42" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41587.599255631074</v>
       </c>
       <c r="K42" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L42" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
+      <c r="N42" s="16"/>
       <c r="O42" s="14"/>
       <c r="P42" s="13"/>
       <c r="Q42" s="13"/>
@@ -3365,18 +3300,16 @@
         <v>1</v>
       </c>
       <c r="J43" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41740.46567428796</v>
       </c>
       <c r="K43" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L43" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M43" s="14"/>
-      <c r="N43" s="14"/>
+      <c r="N43" s="16"/>
       <c r="O43" s="14"/>
       <c r="P43" s="13"/>
       <c r="Q43" s="13"/>
@@ -3414,18 +3347,16 @@
         <v>1</v>
       </c>
       <c r="J44" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41725.001431946534</v>
       </c>
       <c r="K44" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L44" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
+      <c r="N44" s="16"/>
       <c r="O44" s="14"/>
       <c r="P44" s="13"/>
       <c r="Q44" s="13"/>
@@ -3463,18 +3394,16 @@
         <v>1</v>
       </c>
       <c r="J45" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41849.934868238532</v>
       </c>
       <c r="K45" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L45" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M45" s="14"/>
-      <c r="N45" s="14"/>
+      <c r="N45" s="16"/>
       <c r="O45" s="14"/>
       <c r="P45" s="13"/>
       <c r="Q45" s="13"/>
@@ -3512,18 +3441,16 @@
         <v>1</v>
       </c>
       <c r="J46" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41810.296910406032</v>
       </c>
       <c r="K46" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L46" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M46" s="14"/>
-      <c r="N46" s="14"/>
+      <c r="N46" s="16"/>
       <c r="O46" s="14"/>
       <c r="P46" s="13"/>
       <c r="Q46" s="13"/>
@@ -3561,18 +3488,16 @@
         <v>1</v>
       </c>
       <c r="J47" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41793.690558487498</v>
       </c>
       <c r="K47" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L47" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M47" s="14"/>
-      <c r="N47" s="14"/>
+      <c r="N47" s="16"/>
       <c r="O47" s="14"/>
       <c r="P47" s="13"/>
       <c r="Q47" s="13"/>
@@ -3610,18 +3535,16 @@
         <v>1</v>
       </c>
       <c r="J48" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41709.945025018555</v>
       </c>
       <c r="K48" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L48" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
+      <c r="N48" s="16"/>
       <c r="O48" s="14"/>
       <c r="P48" s="13"/>
       <c r="Q48" s="13"/>
@@ -3659,18 +3582,16 @@
         <v>1</v>
       </c>
       <c r="J49" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41466.834886404045</v>
       </c>
       <c r="K49" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L49" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M49" s="14"/>
-      <c r="N49" s="14"/>
+      <c r="N49" s="16"/>
       <c r="O49" s="14"/>
       <c r="P49" s="13"/>
       <c r="Q49" s="13"/>
@@ -3708,18 +3629,16 @@
         <v>1</v>
       </c>
       <c r="J50" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41465.690035932945</v>
       </c>
       <c r="K50" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L50" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M50" s="14"/>
-      <c r="N50" s="14"/>
+      <c r="N50" s="16"/>
       <c r="O50" s="14"/>
       <c r="P50" s="13"/>
       <c r="Q50" s="13"/>
@@ -3757,18 +3676,16 @@
         <v>1</v>
       </c>
       <c r="J51" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41675.29079324755</v>
       </c>
       <c r="K51" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L51" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
+      <c r="N51" s="16"/>
       <c r="O51" s="14"/>
       <c r="P51" s="13"/>
       <c r="Q51" s="13"/>
@@ -3806,18 +3723,16 @@
         <v>1</v>
       </c>
       <c r="J52" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41694.205537681795</v>
       </c>
       <c r="K52" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L52" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M52" s="14"/>
-      <c r="N52" s="14"/>
+      <c r="N52" s="16"/>
       <c r="O52" s="14"/>
       <c r="P52" s="13"/>
       <c r="Q52" s="13"/>
@@ -3855,18 +3770,16 @@
         <v>1</v>
       </c>
       <c r="J53" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41536.945070884853</v>
       </c>
       <c r="K53" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L53" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
+      <c r="N53" s="16"/>
       <c r="O53" s="14"/>
       <c r="P53" s="13"/>
       <c r="Q53" s="13"/>
@@ -3904,18 +3817,16 @@
         <v>1</v>
       </c>
       <c r="J54" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41637.268167380913</v>
       </c>
       <c r="K54" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L54" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M54" s="14"/>
-      <c r="N54" s="14"/>
+      <c r="N54" s="16"/>
       <c r="O54" s="14"/>
       <c r="P54" s="13"/>
       <c r="Q54" s="13"/>
@@ -3953,18 +3864,16 @@
         <v>1</v>
       </c>
       <c r="J55" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41534.286542546019</v>
       </c>
       <c r="K55" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L55" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M55" s="14"/>
-      <c r="N55" s="14"/>
+      <c r="N55" s="16"/>
       <c r="O55" s="14"/>
       <c r="P55" s="13"/>
       <c r="Q55" s="13"/>
@@ -4002,18 +3911,16 @@
         <v>1</v>
       </c>
       <c r="J56" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41770.224659801417</v>
       </c>
       <c r="K56" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L56" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M56" s="14"/>
-      <c r="N56" s="14"/>
+      <c r="N56" s="16"/>
       <c r="O56" s="14"/>
       <c r="P56" s="13"/>
       <c r="Q56" s="13"/>
@@ -4051,18 +3958,16 @@
         <v>1</v>
       </c>
       <c r="J57" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41647.234935802349</v>
       </c>
       <c r="K57" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L57" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M57" s="14"/>
-      <c r="N57" s="14"/>
+      <c r="N57" s="16"/>
       <c r="O57" s="14"/>
       <c r="P57" s="13"/>
       <c r="Q57" s="13"/>
@@ -4100,18 +4005,16 @@
         <v>1</v>
       </c>
       <c r="J58" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41755.251313357869</v>
       </c>
       <c r="K58" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L58" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M58" s="14"/>
-      <c r="N58" s="14"/>
+      <c r="N58" s="16"/>
       <c r="O58" s="14"/>
       <c r="P58" s="13"/>
       <c r="Q58" s="13"/>
@@ -4149,18 +4052,16 @@
         <v>1</v>
       </c>
       <c r="J59" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41560.371818894426</v>
       </c>
       <c r="K59" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L59" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M59" s="14"/>
-      <c r="N59" s="14"/>
+      <c r="N59" s="16"/>
       <c r="O59" s="14"/>
       <c r="P59" s="13"/>
       <c r="Q59" s="13"/>
@@ -4198,18 +4099,16 @@
         <v>1</v>
       </c>
       <c r="J60" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41473.545062395126</v>
       </c>
       <c r="K60" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L60" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
+      <c r="N60" s="16"/>
       <c r="O60" s="14"/>
       <c r="P60" s="13"/>
       <c r="Q60" s="13"/>
@@ -4247,18 +4146,16 @@
         <v>1</v>
       </c>
       <c r="J61" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41500.603145190093</v>
       </c>
       <c r="K61" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L61" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M61" s="14"/>
-      <c r="N61" s="14"/>
+      <c r="N61" s="16"/>
       <c r="O61" s="14"/>
       <c r="P61" s="13"/>
       <c r="Q61" s="13"/>
@@ -4296,18 +4193,16 @@
         <v>1</v>
       </c>
       <c r="J62" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41811.44254929731</v>
       </c>
       <c r="K62" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L62" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
+      <c r="N62" s="16"/>
       <c r="O62" s="14"/>
       <c r="P62" s="13"/>
       <c r="Q62" s="13"/>
@@ -4345,18 +4240,16 @@
         <v>1</v>
       </c>
       <c r="J63" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41708.410607279497</v>
       </c>
       <c r="K63" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L63" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M63" s="14"/>
-      <c r="N63" s="14"/>
+      <c r="N63" s="16"/>
       <c r="O63" s="14"/>
       <c r="P63" s="13"/>
       <c r="Q63" s="13"/>
@@ -4394,18 +4287,16 @@
         <v>1</v>
       </c>
       <c r="J64" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41683.343415540556</v>
       </c>
       <c r="K64" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L64" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M64" s="14"/>
-      <c r="N64" s="14"/>
+      <c r="N64" s="16"/>
       <c r="O64" s="14"/>
       <c r="P64" s="13"/>
       <c r="Q64" s="13"/>
@@ -4443,18 +4334,16 @@
         <v>1</v>
       </c>
       <c r="J65" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41625.32407330368</v>
       </c>
       <c r="K65" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L65" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M65" s="14"/>
-      <c r="N65" s="14"/>
+      <c r="N65" s="16"/>
       <c r="O65" s="14"/>
       <c r="P65" s="13"/>
       <c r="Q65" s="13"/>
@@ -4492,18 +4381,16 @@
         <v>1</v>
       </c>
       <c r="J66" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41775.074506466874</v>
       </c>
       <c r="K66" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L66" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M66" s="14"/>
-      <c r="N66" s="14"/>
+      <c r="N66" s="16"/>
       <c r="O66" s="14"/>
       <c r="P66" s="13"/>
       <c r="Q66" s="13"/>
@@ -4541,18 +4428,16 @@
         <v>1</v>
       </c>
       <c r="J67" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41477.727567616348</v>
       </c>
       <c r="K67" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L67" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M67" s="14"/>
-      <c r="N67" s="14"/>
+      <c r="N67" s="16"/>
       <c r="O67" s="14"/>
       <c r="P67" s="13"/>
       <c r="Q67" s="13"/>
@@ -4590,18 +4475,16 @@
         <v>1</v>
       </c>
       <c r="J68" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41730.171732443763</v>
       </c>
       <c r="K68" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L68" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M68" s="14"/>
-      <c r="N68" s="14"/>
+      <c r="N68" s="16"/>
       <c r="O68" s="14"/>
       <c r="P68" s="13"/>
       <c r="Q68" s="13"/>
@@ -4639,18 +4522,16 @@
         <v>1</v>
       </c>
       <c r="J69" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41861.73707495736</v>
       </c>
       <c r="K69" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L69" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M69" s="14"/>
-      <c r="N69" s="14"/>
+      <c r="N69" s="16"/>
       <c r="O69" s="14"/>
       <c r="P69" s="13"/>
       <c r="Q69" s="13"/>
@@ -4688,18 +4569,16 @@
         <v>1</v>
       </c>
       <c r="J70" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41553.373307931412</v>
       </c>
       <c r="K70" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L70" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M70" s="14"/>
-      <c r="N70" s="14"/>
+      <c r="N70" s="16"/>
       <c r="O70" s="14"/>
       <c r="P70" s="13"/>
       <c r="Q70" s="13"/>
@@ -4737,18 +4616,16 @@
         <v>1</v>
       </c>
       <c r="J71" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41595.555871816454</v>
       </c>
       <c r="K71" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L71" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M71" s="14"/>
-      <c r="N71" s="14"/>
+      <c r="N71" s="16"/>
       <c r="O71" s="14"/>
       <c r="P71" s="13"/>
       <c r="Q71" s="13"/>
@@ -4786,18 +4663,16 @@
         <v>1</v>
       </c>
       <c r="J72" s="15">
-        <f t="shared" si="0"/>
-        <v>41666.666666666664</v>
+        <v>41776.231269062708</v>
       </c>
       <c r="K72" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L72" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M72" s="14"/>
-      <c r="N72" s="14"/>
+      <c r="N72" s="16"/>
       <c r="O72" s="14"/>
       <c r="P72" s="13"/>
       <c r="Q72" s="13"/>
@@ -4835,18 +4710,16 @@
         <v>1</v>
       </c>
       <c r="J73" s="15">
-        <f t="shared" ref="J73:J82" si="1">AVERAGE(900,1600)*1000/30</f>
-        <v>41666.666666666664</v>
+        <v>41575.361342047931</v>
       </c>
       <c r="K73" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L73" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M73" s="14"/>
-      <c r="N73" s="14"/>
+      <c r="N73" s="16"/>
       <c r="O73" s="14"/>
       <c r="P73" s="13"/>
       <c r="Q73" s="13"/>
@@ -4884,18 +4757,16 @@
         <v>1</v>
       </c>
       <c r="J74" s="15">
-        <f t="shared" si="1"/>
-        <v>41666.666666666664</v>
+        <v>41481.720151521869</v>
       </c>
       <c r="K74" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L74" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M74" s="14"/>
-      <c r="N74" s="14"/>
+      <c r="N74" s="16"/>
       <c r="O74" s="14"/>
       <c r="P74" s="13"/>
       <c r="Q74" s="13"/>
@@ -4933,18 +4804,16 @@
         <v>1</v>
       </c>
       <c r="J75" s="15">
-        <f t="shared" si="1"/>
-        <v>41666.666666666664</v>
+        <v>41525.622724595647</v>
       </c>
       <c r="K75" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L75" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M75" s="14"/>
-      <c r="N75" s="14"/>
+      <c r="N75" s="16"/>
       <c r="O75" s="14"/>
       <c r="P75" s="13"/>
       <c r="Q75" s="13"/>
@@ -4982,18 +4851,16 @@
         <v>1</v>
       </c>
       <c r="J76" s="15">
-        <f t="shared" si="1"/>
-        <v>41666.666666666664</v>
+        <v>41865.444555121139</v>
       </c>
       <c r="K76" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L76" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M76" s="14"/>
-      <c r="N76" s="14"/>
+      <c r="N76" s="16"/>
       <c r="O76" s="14"/>
       <c r="P76" s="13"/>
       <c r="Q76" s="13"/>
@@ -5031,18 +4898,16 @@
         <v>1</v>
       </c>
       <c r="J77" s="15">
-        <f t="shared" si="1"/>
-        <v>41666.666666666664</v>
+        <v>41837.685515223915</v>
       </c>
       <c r="K77" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L77" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M77" s="14"/>
-      <c r="N77" s="14"/>
+      <c r="N77" s="16"/>
       <c r="O77" s="14"/>
       <c r="P77" s="13"/>
       <c r="Q77" s="13"/>
@@ -5080,18 +4945,16 @@
         <v>1</v>
       </c>
       <c r="J78" s="15">
-        <f t="shared" si="1"/>
-        <v>41666.666666666664</v>
+        <v>41726.575735597442</v>
       </c>
       <c r="K78" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L78" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M78" s="14"/>
-      <c r="N78" s="14"/>
+      <c r="N78" s="16"/>
       <c r="O78" s="14"/>
       <c r="P78" s="13"/>
       <c r="Q78" s="13"/>
@@ -5129,18 +4992,16 @@
         <v>1</v>
       </c>
       <c r="J79" s="15">
-        <f t="shared" si="1"/>
-        <v>41666.666666666664</v>
+        <v>41674.561504628095</v>
       </c>
       <c r="K79" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L79" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M79" s="14"/>
-      <c r="N79" s="14"/>
+      <c r="N79" s="16"/>
       <c r="O79" s="14"/>
       <c r="P79" s="13"/>
       <c r="Q79" s="13"/>
@@ -5178,18 +5039,16 @@
         <v>1</v>
       </c>
       <c r="J80" s="15">
-        <f t="shared" si="1"/>
-        <v>41666.666666666664</v>
+        <v>41474.043794179677</v>
       </c>
       <c r="K80" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L80" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M80" s="14"/>
-      <c r="N80" s="14"/>
+      <c r="N80" s="16"/>
       <c r="O80" s="14"/>
       <c r="P80" s="13"/>
       <c r="Q80" s="13"/>
@@ -5227,18 +5086,16 @@
         <v>1</v>
       </c>
       <c r="J81" s="15">
-        <f t="shared" si="1"/>
-        <v>41666.666666666664</v>
+        <v>41730.826742041798</v>
       </c>
       <c r="K81" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L81" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M81" s="14"/>
-      <c r="N81" s="14"/>
+      <c r="N81" s="16"/>
       <c r="O81" s="14"/>
       <c r="P81" s="13"/>
       <c r="Q81" s="13"/>
@@ -5276,18 +5133,16 @@
         <v>1</v>
       </c>
       <c r="J82" s="15">
-        <f t="shared" si="1"/>
-        <v>41666.666666666664</v>
+        <v>41479.694519694502</v>
       </c>
       <c r="K82" s="15">
-        <f>0</f>
         <v>0</v>
       </c>
       <c r="L82" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="M82" s="14"/>
-      <c r="N82" s="14"/>
+      <c r="N82" s="16"/>
       <c r="O82" s="14"/>
       <c r="P82" s="13"/>
       <c r="Q82" s="13"/>
@@ -5325,18 +5180,16 @@
         <v>1</v>
       </c>
       <c r="J83" s="15">
-        <f>AVERAGE(1300,1900)*1000/25</f>
-        <v>64000</v>
+        <v>63801.889038465662</v>
       </c>
       <c r="K83" s="15">
-        <f>0.007*1000</f>
-        <v>7</v>
+        <v>7.0223566071828891</v>
       </c>
       <c r="L83" s="16">
         <v>0.25</v>
       </c>
       <c r="M83" s="14"/>
-      <c r="N83" s="14"/>
+      <c r="N83" s="16"/>
       <c r="O83" s="14"/>
       <c r="P83" s="13"/>
       <c r="Q83" s="13"/>
@@ -5374,18 +5227,16 @@
         <v>1</v>
       </c>
       <c r="J84" s="15">
-        <f t="shared" ref="J84:J99" si="2">AVERAGE(1300,1900)*1000/25</f>
-        <v>64000</v>
+        <v>63869.012555425106</v>
       </c>
       <c r="K84" s="15">
-        <f t="shared" ref="K84:K99" si="3">0.007*1000</f>
-        <v>7</v>
+        <v>6.9913537805586952</v>
       </c>
       <c r="L84" s="16">
         <v>0.25</v>
       </c>
       <c r="M84" s="14"/>
-      <c r="N84" s="14"/>
+      <c r="N84" s="16"/>
       <c r="O84" s="14"/>
       <c r="P84" s="13"/>
       <c r="Q84" s="13"/>
@@ -5423,18 +5274,16 @@
         <v>1</v>
       </c>
       <c r="J85" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>64142.754101035134</v>
       </c>
       <c r="K85" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>7.0158395924675858</v>
       </c>
       <c r="L85" s="16">
         <v>0.25</v>
       </c>
       <c r="M85" s="14"/>
-      <c r="N85" s="14"/>
+      <c r="N85" s="16"/>
       <c r="O85" s="14"/>
       <c r="P85" s="13"/>
       <c r="Q85" s="13"/>
@@ -5472,18 +5321,16 @@
         <v>1</v>
       </c>
       <c r="J86" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>64116.673662474852</v>
       </c>
       <c r="K86" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>7.0211878618545596</v>
       </c>
       <c r="L86" s="16">
         <v>0.25</v>
       </c>
       <c r="M86" s="14"/>
-      <c r="N86" s="14"/>
+      <c r="N86" s="16"/>
       <c r="O86" s="14"/>
       <c r="P86" s="13"/>
       <c r="Q86" s="13"/>
@@ -5521,18 +5368,16 @@
         <v>1</v>
       </c>
       <c r="J87" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>64093.096594265233</v>
       </c>
       <c r="K87" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>7.0152008170788624</v>
       </c>
       <c r="L87" s="16">
         <v>0.25</v>
       </c>
       <c r="M87" s="14"/>
-      <c r="N87" s="14"/>
+      <c r="N87" s="16"/>
       <c r="O87" s="14"/>
       <c r="P87" s="13"/>
       <c r="Q87" s="13"/>
@@ -5570,18 +5415,16 @@
         <v>1</v>
       </c>
       <c r="J88" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>64273.819418383937</v>
       </c>
       <c r="K88" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>7.0069609895724545</v>
       </c>
       <c r="L88" s="16">
         <v>0.25</v>
       </c>
       <c r="M88" s="14"/>
-      <c r="N88" s="14"/>
+      <c r="N88" s="16"/>
       <c r="O88" s="14"/>
       <c r="P88" s="13"/>
       <c r="Q88" s="13"/>
@@ -5619,18 +5462,16 @@
         <v>1</v>
       </c>
       <c r="J89" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>64000.844612205117</v>
       </c>
       <c r="K89" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6.9913480086750397</v>
       </c>
       <c r="L89" s="16">
         <v>0.25</v>
       </c>
       <c r="M89" s="14"/>
-      <c r="N89" s="14"/>
+      <c r="N89" s="16"/>
       <c r="O89" s="14"/>
       <c r="P89" s="13"/>
       <c r="Q89" s="13"/>
@@ -5668,18 +5509,16 @@
         <v>1</v>
       </c>
       <c r="J90" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>63897.609198459417</v>
       </c>
       <c r="K90" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>7.0131833059973214</v>
       </c>
       <c r="L90" s="16">
         <v>0.25</v>
       </c>
       <c r="M90" s="14"/>
-      <c r="N90" s="14"/>
+      <c r="N90" s="16"/>
       <c r="O90" s="14"/>
       <c r="P90" s="13"/>
       <c r="Q90" s="13"/>
@@ -5717,18 +5556,16 @@
         <v>1</v>
       </c>
       <c r="J91" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>64235.472072003387</v>
       </c>
       <c r="K91" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6.9884744586752676</v>
       </c>
       <c r="L91" s="16">
         <v>0.25</v>
       </c>
       <c r="M91" s="14"/>
-      <c r="N91" s="14"/>
+      <c r="N91" s="16"/>
       <c r="O91" s="14"/>
       <c r="P91" s="13"/>
       <c r="Q91" s="13"/>
@@ -5766,18 +5603,16 @@
         <v>1</v>
       </c>
       <c r="J92" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>64070.545509375268</v>
       </c>
       <c r="K92" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>7.0080776694357461</v>
       </c>
       <c r="L92" s="16">
         <v>0.25</v>
       </c>
       <c r="M92" s="14"/>
-      <c r="N92" s="14"/>
+      <c r="N92" s="16"/>
       <c r="O92" s="14"/>
       <c r="P92" s="13"/>
       <c r="Q92" s="13"/>
@@ -5815,18 +5650,16 @@
         <v>1</v>
       </c>
       <c r="J93" s="15">
-        <f>AVERAGE(1300,1900)*1000/25</f>
-        <v>64000</v>
+        <v>64027.9130543297</v>
       </c>
       <c r="K93" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6.9847203773009401</v>
       </c>
       <c r="L93" s="16">
         <v>0.25</v>
       </c>
       <c r="M93" s="14"/>
-      <c r="N93" s="14"/>
+      <c r="N93" s="16"/>
       <c r="O93" s="14"/>
       <c r="P93" s="13"/>
       <c r="Q93" s="13"/>
@@ -5864,18 +5697,16 @@
         <v>1</v>
       </c>
       <c r="J94" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>64266.8607002922</v>
       </c>
       <c r="K94" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>7.0236443157007491</v>
       </c>
       <c r="L94" s="16">
         <v>0.25</v>
       </c>
       <c r="M94" s="14"/>
-      <c r="N94" s="14"/>
+      <c r="N94" s="16"/>
       <c r="O94" s="14"/>
       <c r="P94" s="13"/>
       <c r="Q94" s="13"/>
@@ -5913,18 +5744,16 @@
         <v>1</v>
       </c>
       <c r="J95" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>63864.543558127749</v>
       </c>
       <c r="K95" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6.9912166915016902</v>
       </c>
       <c r="L95" s="16">
         <v>0.25</v>
       </c>
       <c r="M95" s="14"/>
-      <c r="N95" s="14"/>
+      <c r="N95" s="16"/>
       <c r="O95" s="14"/>
       <c r="P95" s="13"/>
       <c r="Q95" s="13"/>
@@ -5962,18 +5791,16 @@
         <v>1</v>
       </c>
       <c r="J96" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>64151.814917641204</v>
       </c>
       <c r="K96" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6.9931830897586176</v>
       </c>
       <c r="L96" s="16">
         <v>0.25</v>
       </c>
       <c r="M96" s="14"/>
-      <c r="N96" s="14"/>
+      <c r="N96" s="16"/>
       <c r="O96" s="14"/>
       <c r="P96" s="13"/>
       <c r="Q96" s="13"/>
@@ -6011,18 +5838,16 @@
         <v>1</v>
       </c>
       <c r="J97" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>63814.679822614853</v>
       </c>
       <c r="K97" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>7.022585709864912</v>
       </c>
       <c r="L97" s="16">
         <v>0.25</v>
       </c>
       <c r="M97" s="14"/>
-      <c r="N97" s="14"/>
+      <c r="N97" s="16"/>
       <c r="O97" s="14"/>
       <c r="P97" s="13"/>
       <c r="Q97" s="13"/>
@@ -6060,18 +5885,16 @@
         <v>1</v>
       </c>
       <c r="J98" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>63844.11228008481</v>
       </c>
       <c r="K98" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6.9693692726856034</v>
       </c>
       <c r="L98" s="16">
         <v>0.25</v>
       </c>
       <c r="M98" s="14"/>
-      <c r="N98" s="14"/>
+      <c r="N98" s="16"/>
       <c r="O98" s="14"/>
       <c r="P98" s="13"/>
       <c r="Q98" s="13"/>
@@ -6109,18 +5932,16 @@
         <v>1</v>
       </c>
       <c r="J99" s="15">
-        <f t="shared" si="2"/>
-        <v>64000</v>
+        <v>64077.844325403275</v>
       </c>
       <c r="K99" s="15">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <v>6.9768601821858303</v>
       </c>
       <c r="L99" s="16">
         <v>0.25</v>
       </c>
       <c r="M99" s="14"/>
-      <c r="N99" s="14"/>
+      <c r="N99" s="16"/>
       <c r="O99" s="14"/>
       <c r="P99" s="13"/>
       <c r="Q99" s="13"/>
@@ -6158,17 +5979,16 @@
         <v>1</v>
       </c>
       <c r="J100" s="15">
-        <f>2336*1000/100</f>
-        <v>23360</v>
+        <v>23282.114066894279</v>
       </c>
       <c r="K100" s="15">
-        <v>0.1</v>
+        <v>0.10045030288901147</v>
       </c>
       <c r="L100" s="16">
         <v>0.25</v>
       </c>
       <c r="M100" s="14"/>
-      <c r="N100" s="14"/>
+      <c r="N100" s="16"/>
       <c r="O100" s="14"/>
       <c r="P100" s="13"/>
       <c r="Q100" s="13"/>
@@ -6206,17 +6026,16 @@
         <v>1</v>
       </c>
       <c r="J101" s="15">
-        <f t="shared" ref="J101:J127" si="4">2336*1000/100</f>
-        <v>23360</v>
+        <v>23331.758312287424</v>
       </c>
       <c r="K101" s="15">
-        <v>0.1</v>
+        <v>0.10009008691714137</v>
       </c>
       <c r="L101" s="16">
         <v>0.25</v>
       </c>
       <c r="M101" s="14"/>
-      <c r="N101" s="14"/>
+      <c r="N101" s="16"/>
       <c r="O101" s="14"/>
       <c r="P101" s="13"/>
       <c r="Q101" s="13"/>
@@ -6254,17 +6073,16 @@
         <v>1</v>
       </c>
       <c r="J102" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23324.004007406813</v>
       </c>
       <c r="K102" s="15">
-        <v>0.1</v>
+        <v>9.9958651132427773E-2</v>
       </c>
       <c r="L102" s="16">
         <v>0.25</v>
       </c>
       <c r="M102" s="14"/>
-      <c r="N102" s="14"/>
+      <c r="N102" s="16"/>
       <c r="O102" s="14"/>
       <c r="P102" s="13"/>
       <c r="Q102" s="13"/>
@@ -6302,17 +6120,16 @@
         <v>1</v>
       </c>
       <c r="J103" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23396.455200996934</v>
       </c>
       <c r="K103" s="15">
-        <v>0.1</v>
+        <v>0.10049429428769217</v>
       </c>
       <c r="L103" s="16">
         <v>0.25</v>
       </c>
       <c r="M103" s="14"/>
-      <c r="N103" s="14"/>
+      <c r="N103" s="16"/>
       <c r="O103" s="14"/>
       <c r="P103" s="13"/>
       <c r="Q103" s="13"/>
@@ -6350,17 +6167,16 @@
         <v>1</v>
       </c>
       <c r="J104" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23318.84393617684</v>
       </c>
       <c r="K104" s="15">
-        <v>0.1</v>
+        <v>9.9752627515339254E-2</v>
       </c>
       <c r="L104" s="16">
         <v>0.25</v>
       </c>
       <c r="M104" s="14"/>
-      <c r="N104" s="14"/>
+      <c r="N104" s="16"/>
       <c r="O104" s="14"/>
       <c r="P104" s="13"/>
       <c r="Q104" s="13"/>
@@ -6398,17 +6214,16 @@
         <v>1</v>
       </c>
       <c r="J105" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23441.973159096651</v>
       </c>
       <c r="K105" s="15">
-        <v>0.1</v>
+        <v>0.10015252632930144</v>
       </c>
       <c r="L105" s="16">
         <v>0.25</v>
       </c>
       <c r="M105" s="14"/>
-      <c r="N105" s="14"/>
+      <c r="N105" s="16"/>
       <c r="O105" s="14"/>
       <c r="P105" s="13"/>
       <c r="Q105" s="13"/>
@@ -6446,17 +6261,16 @@
         <v>1</v>
       </c>
       <c r="J106" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23326.756776857404</v>
       </c>
       <c r="K106" s="15">
-        <v>0.1</v>
+        <v>9.952838164045763E-2</v>
       </c>
       <c r="L106" s="16">
         <v>0.25</v>
       </c>
       <c r="M106" s="14"/>
-      <c r="N106" s="14"/>
+      <c r="N106" s="16"/>
       <c r="O106" s="14"/>
       <c r="P106" s="13"/>
       <c r="Q106" s="13"/>
@@ -6494,17 +6308,16 @@
         <v>1</v>
       </c>
       <c r="J107" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23468.399585805146</v>
       </c>
       <c r="K107" s="15">
-        <v>0.1</v>
+        <v>9.9955751620313241E-2</v>
       </c>
       <c r="L107" s="16">
         <v>0.25</v>
       </c>
       <c r="M107" s="14"/>
-      <c r="N107" s="14"/>
+      <c r="N107" s="16"/>
       <c r="O107" s="14"/>
       <c r="P107" s="13"/>
       <c r="Q107" s="13"/>
@@ -6542,17 +6355,16 @@
         <v>1</v>
       </c>
       <c r="J108" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23441.845688753809</v>
       </c>
       <c r="K108" s="15">
-        <v>0.1</v>
+        <v>0.10017306151438897</v>
       </c>
       <c r="L108" s="16">
         <v>0.25</v>
       </c>
       <c r="M108" s="14"/>
-      <c r="N108" s="14"/>
+      <c r="N108" s="16"/>
       <c r="O108" s="14"/>
       <c r="P108" s="13"/>
       <c r="Q108" s="13"/>
@@ -6590,17 +6402,16 @@
         <v>1</v>
       </c>
       <c r="J109" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23310.004289913501</v>
       </c>
       <c r="K109" s="15">
-        <v>0.1</v>
+        <v>9.9748269280810709E-2</v>
       </c>
       <c r="L109" s="16">
         <v>0.25</v>
       </c>
       <c r="M109" s="14"/>
-      <c r="N109" s="14"/>
+      <c r="N109" s="16"/>
       <c r="O109" s="14"/>
       <c r="P109" s="13"/>
       <c r="Q109" s="13"/>
@@ -6638,17 +6449,16 @@
         <v>1</v>
       </c>
       <c r="J110" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23476.251430980188</v>
       </c>
       <c r="K110" s="15">
-        <v>0.1</v>
+        <v>9.9767426247155636E-2</v>
       </c>
       <c r="L110" s="16">
         <v>0.25</v>
       </c>
       <c r="M110" s="14"/>
-      <c r="N110" s="14"/>
+      <c r="N110" s="16"/>
       <c r="O110" s="14"/>
       <c r="P110" s="13"/>
       <c r="Q110" s="13"/>
@@ -6686,17 +6496,16 @@
         <v>1</v>
       </c>
       <c r="J111" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23371.605505223153</v>
       </c>
       <c r="K111" s="15">
-        <v>0.1</v>
+        <v>9.9770349390131213E-2</v>
       </c>
       <c r="L111" s="16">
         <v>0.25</v>
       </c>
       <c r="M111" s="14"/>
-      <c r="N111" s="14"/>
+      <c r="N111" s="16"/>
       <c r="O111" s="14"/>
       <c r="P111" s="13"/>
       <c r="Q111" s="13"/>
@@ -6734,17 +6543,16 @@
         <v>1</v>
       </c>
       <c r="J112" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23403.973941747761</v>
       </c>
       <c r="K112" s="15">
-        <v>0.1</v>
+        <v>9.9505394570653549E-2</v>
       </c>
       <c r="L112" s="16">
         <v>0.25</v>
       </c>
       <c r="M112" s="14"/>
-      <c r="N112" s="14"/>
+      <c r="N112" s="16"/>
       <c r="O112" s="14"/>
       <c r="P112" s="13"/>
       <c r="Q112" s="13"/>
@@ -6782,17 +6590,16 @@
         <v>1</v>
       </c>
       <c r="J113" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23351.057719377699</v>
       </c>
       <c r="K113" s="15">
-        <v>0.1</v>
+        <v>9.9835141860253371E-2</v>
       </c>
       <c r="L113" s="16">
         <v>0.25</v>
       </c>
       <c r="M113" s="14"/>
-      <c r="N113" s="14"/>
+      <c r="N113" s="16"/>
       <c r="O113" s="14"/>
       <c r="P113" s="13"/>
       <c r="Q113" s="13"/>
@@ -6830,17 +6637,16 @@
         <v>1</v>
       </c>
       <c r="J114" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23304.979234092883</v>
       </c>
       <c r="K114" s="15">
-        <v>0.1</v>
+        <v>9.9964003235930729E-2</v>
       </c>
       <c r="L114" s="16">
         <v>0.25</v>
       </c>
       <c r="M114" s="14"/>
-      <c r="N114" s="14"/>
+      <c r="N114" s="16"/>
       <c r="O114" s="14"/>
       <c r="P114" s="13"/>
       <c r="Q114" s="13"/>
@@ -6878,17 +6684,16 @@
         <v>1</v>
       </c>
       <c r="J115" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23364.466660647377</v>
       </c>
       <c r="K115" s="15">
-        <v>0.1</v>
+        <v>0.10041072332178778</v>
       </c>
       <c r="L115" s="16">
         <v>0.25</v>
       </c>
       <c r="M115" s="14"/>
-      <c r="N115" s="14"/>
+      <c r="N115" s="16"/>
       <c r="O115" s="14"/>
       <c r="P115" s="13"/>
       <c r="Q115" s="13"/>
@@ -6926,17 +6731,16 @@
         <v>1</v>
       </c>
       <c r="J116" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23400.653918159165</v>
       </c>
       <c r="K116" s="15">
-        <v>0.1</v>
+        <v>9.9542769947627799E-2</v>
       </c>
       <c r="L116" s="16">
         <v>0.25</v>
       </c>
       <c r="M116" s="14"/>
-      <c r="N116" s="14"/>
+      <c r="N116" s="16"/>
       <c r="O116" s="14"/>
       <c r="P116" s="13"/>
       <c r="Q116" s="13"/>
@@ -6974,17 +6778,16 @@
         <v>1</v>
       </c>
       <c r="J117" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23295.63776040325</v>
       </c>
       <c r="K117" s="15">
-        <v>0.1</v>
+        <v>0.10026152610256052</v>
       </c>
       <c r="L117" s="16">
         <v>0.25</v>
       </c>
       <c r="M117" s="14"/>
-      <c r="N117" s="14"/>
+      <c r="N117" s="16"/>
       <c r="O117" s="14"/>
       <c r="P117" s="13"/>
       <c r="Q117" s="13"/>
@@ -7022,17 +6825,16 @@
         <v>1</v>
       </c>
       <c r="J118" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23411.297727511683</v>
       </c>
       <c r="K118" s="15">
-        <v>0.1</v>
+        <v>0.10033559839334896</v>
       </c>
       <c r="L118" s="16">
         <v>0.25</v>
       </c>
       <c r="M118" s="14"/>
-      <c r="N118" s="14"/>
+      <c r="N118" s="16"/>
       <c r="O118" s="14"/>
       <c r="P118" s="13"/>
       <c r="Q118" s="13"/>
@@ -7070,17 +6872,16 @@
         <v>1</v>
       </c>
       <c r="J119" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23360.065218580319</v>
       </c>
       <c r="K119" s="15">
-        <v>0.1</v>
+        <v>9.9702625556489691E-2</v>
       </c>
       <c r="L119" s="16">
         <v>0.25</v>
       </c>
       <c r="M119" s="14"/>
-      <c r="N119" s="14"/>
+      <c r="N119" s="16"/>
       <c r="O119" s="14"/>
       <c r="P119" s="13"/>
       <c r="Q119" s="13"/>
@@ -7118,17 +6919,16 @@
         <v>1</v>
       </c>
       <c r="J120" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23464.956226849928</v>
       </c>
       <c r="K120" s="15">
-        <v>0.1</v>
+        <v>0.10022658269665174</v>
       </c>
       <c r="L120" s="16">
         <v>0.25</v>
       </c>
       <c r="M120" s="14"/>
-      <c r="N120" s="14"/>
+      <c r="N120" s="16"/>
       <c r="O120" s="14"/>
       <c r="P120" s="13"/>
       <c r="Q120" s="13"/>
@@ -7166,17 +6966,16 @@
         <v>1</v>
       </c>
       <c r="J121" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23390.00535466124</v>
       </c>
       <c r="K121" s="15">
-        <v>0.1</v>
+        <v>0.10029751161489081</v>
       </c>
       <c r="L121" s="16">
         <v>0.25</v>
       </c>
       <c r="M121" s="14"/>
-      <c r="N121" s="14"/>
+      <c r="N121" s="16"/>
       <c r="O121" s="14"/>
       <c r="P121" s="13"/>
       <c r="Q121" s="13"/>
@@ -7214,17 +7013,16 @@
         <v>1</v>
       </c>
       <c r="J122" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23414.897768218761</v>
       </c>
       <c r="K122" s="15">
-        <v>0.1</v>
+        <v>0.10028326352450577</v>
       </c>
       <c r="L122" s="16">
         <v>0.25</v>
       </c>
       <c r="M122" s="14"/>
-      <c r="N122" s="14"/>
+      <c r="N122" s="16"/>
       <c r="O122" s="14"/>
       <c r="P122" s="13"/>
       <c r="Q122" s="13"/>
@@ -7262,17 +7060,16 @@
         <v>1</v>
       </c>
       <c r="J123" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23349.793962037984</v>
       </c>
       <c r="K123" s="15">
-        <v>0.1</v>
+        <v>0.10019531739192529</v>
       </c>
       <c r="L123" s="16">
         <v>0.25</v>
       </c>
       <c r="M123" s="14"/>
-      <c r="N123" s="14"/>
+      <c r="N123" s="16"/>
       <c r="O123" s="14"/>
       <c r="P123" s="13"/>
       <c r="Q123" s="13"/>
@@ -7310,17 +7107,16 @@
         <v>1</v>
       </c>
       <c r="J124" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23386.03185111293</v>
       </c>
       <c r="K124" s="15">
-        <v>0.1</v>
+        <v>9.9758770523151172E-2</v>
       </c>
       <c r="L124" s="16">
         <v>0.25</v>
       </c>
       <c r="M124" s="14"/>
-      <c r="N124" s="14"/>
+      <c r="N124" s="16"/>
       <c r="O124" s="14"/>
       <c r="P124" s="13"/>
       <c r="Q124" s="13"/>
@@ -7358,17 +7154,16 @@
         <v>1</v>
       </c>
       <c r="J125" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23375.364499825933</v>
       </c>
       <c r="K125" s="15">
-        <v>0.1</v>
+        <v>0.10011751753324215</v>
       </c>
       <c r="L125" s="16">
         <v>0.25</v>
       </c>
       <c r="M125" s="14"/>
-      <c r="N125" s="14"/>
+      <c r="N125" s="16"/>
       <c r="O125" s="14"/>
       <c r="P125" s="13"/>
       <c r="Q125" s="13"/>
@@ -7406,17 +7201,16 @@
         <v>1</v>
       </c>
       <c r="J126" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23395.104422288718</v>
       </c>
       <c r="K126" s="15">
-        <v>0.1</v>
+        <v>9.9999551902656414E-2</v>
       </c>
       <c r="L126" s="16">
         <v>0.25</v>
       </c>
       <c r="M126" s="14"/>
-      <c r="N126" s="14"/>
+      <c r="N126" s="16"/>
       <c r="O126" s="14"/>
       <c r="P126" s="13"/>
       <c r="Q126" s="13"/>
@@ -7454,17 +7248,16 @@
         <v>1</v>
       </c>
       <c r="J127" s="15">
-        <f t="shared" si="4"/>
-        <v>23360</v>
+        <v>23453.633104108292</v>
       </c>
       <c r="K127" s="15">
-        <v>0.1</v>
+        <v>0.10027987369314117</v>
       </c>
       <c r="L127" s="16">
         <v>0.25</v>
       </c>
       <c r="M127" s="14"/>
-      <c r="N127" s="14"/>
+      <c r="N127" s="16"/>
       <c r="O127" s="14"/>
       <c r="P127" s="13"/>
       <c r="Q127" s="13"/>
